--- a/Tests/AboutMarc/AboutMarc_Pass.xlsx
+++ b/Tests/AboutMarc/AboutMarc_Pass.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_11_MOBILE/?preset=4COL_0</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_2561</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_1920</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_1440</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,79 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_DESKTOP/?preset=2COL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>https://marcjacobs.bynder.com/match/MJ_Filename/20240920_HISTORY_SLICE_12_MOBILE/?preset=2COL_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_2561</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE/?preset=FULL_768</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/about-marc.html</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/SP26_HERO_2_SHOWPAGE_MOBILE/?preset=FULL_0</t>
         </is>
       </c>
     </row>
